--- a/Tables/G_ResInfoTable.xlsx
+++ b/Tables/G_ResInfoTable.xlsx
@@ -413,9 +413,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="8.13"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="28.63"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6230,9 +6233,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="21.88"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11997,9 +12003,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="11.5"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="15.5"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17782,9 +17791,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="4" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="9.38"/>
+    <col customWidth="1" min="4" max="4" width="4.5"/>
     <col customWidth="1" min="5" max="5" width="34.75"/>
-    <col customWidth="1" min="6" max="21" width="12.63"/>
+    <col customWidth="1" min="6" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
